--- a/data/02_Daily_Sheets/Expressions_2026-06-14.xlsx
+++ b/data/02_Daily_Sheets/Expressions_2026-06-14.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,7 +466,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CHI-20260614-001</t>
+          <t>CHI-20260614-005</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -481,39 +481,39 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>获悉</t>
+          <t>座谈会</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>Noun</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>huòxī</t>
+          <t>zuò tán huì</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>알게 되다, 접수하다</t>
+          <t>좌담회, 간담회</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>4月29日，记者从北京市发改委获悉，自2024</t>
+          <t>雄安新区高校建设发展座谈会在河北雄安新区召开。</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>我们刚刚获悉，公司下个月将推出新产品。</t>
+          <t>公司每个季度都会组织一次员工座谈会，听取大家的意见。</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CHI-20260614-002</t>
+          <t>CHI-20260614-006</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>稳稳的幸福</t>
+          <t>刷屏了</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -538,116 +538,22 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>wěnwěn de xìngfú</t>
+          <t>shuā píng le</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>안정적인 행복</t>
+          <t>(인터넷에서) 화면을 도배하다, 화제가 되다</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>十年磨一剑！神仙学校给你稳稳的幸福.</t>
+          <t>留学圈被一所“年轻”的美高刷屏了</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>对很多人来说，一份稳定的工作和健康的家庭就是稳稳的幸福。</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>CHI-20260614-003</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-06-14</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Scraped_News</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>受到关注</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Verb phrase</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>shòudào guānzhù</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>주목받다, 관심을 받다</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>这次受到关注的是在成都高新区双塔双集举办的“胡安·米罗：艺述真言”艺术展。</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>他的新书一上市就受到了广泛关注，销量非常好。</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>CHI-20260614-004</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-06-14</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Scraped_News</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>印象</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Noun</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>yìnxiàng</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>인상</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>却始终没有印象。</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>他给我的第一印象非常好，看起来很专业。</t>
+          <t>昨晚那部电影的预告片在朋友圈刷屏了，大家都想去看。</t>
         </is>
       </c>
     </row>
